--- a/admin/deduction_excel.xlsx
+++ b/admin/deduction_excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\TRINITY\htdocs\nrvs_payroll\admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC9C706-0961-4D45-91F7-521987B043CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDDCBCC-0C03-45B6-8E50-87B51F371EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{15A88CCE-3372-449C-83CE-515127A63710}"/>
   </bookViews>
@@ -20,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Employee Code</t>
   </si>
@@ -91,6 +82,9 @@
   </si>
   <si>
     <t>Other Deduction</t>
+  </si>
+  <si>
+    <t>TDS Deduction</t>
   </si>
 </sst>
 </file>
@@ -490,6 +484,7 @@
     <col min="2" max="2" width="18.85546875" style="3" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -504,6 +499,9 @@
         <v>17</v>
       </c>
       <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
         <v>18</v>
       </c>
       <c r="AC1" s="1"/>
@@ -521,6 +519,9 @@
       <c r="D2">
         <v>300</v>
       </c>
+      <c r="E2">
+        <v>400</v>
+      </c>
       <c r="AC2" s="1"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
@@ -536,6 +537,9 @@
       <c r="D3">
         <v>400</v>
       </c>
+      <c r="E3">
+        <v>150</v>
+      </c>
       <c r="AC3" s="1"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -550,6 +554,9 @@
       </c>
       <c r="D4">
         <v>320</v>
+      </c>
+      <c r="E4">
+        <v>460</v>
       </c>
       <c r="AC4" s="1"/>
     </row>

--- a/admin/deduction_excel.xlsx
+++ b/admin/deduction_excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\TRINITY\htdocs\nrvs_payroll\admin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\trinity\htdocs\nrvs_payroll\admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDDCBCC-0C03-45B6-8E50-87B51F371EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8CAD72-B960-4AC9-8328-CD49B832151C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{15A88CCE-3372-449C-83CE-515127A63710}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Employee Code</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>Other Deduction</t>
-  </si>
-  <si>
-    <t>TDS Deduction</t>
   </si>
 </sst>
 </file>
@@ -477,18 +474,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A7F1150-C24C-4C72-9BBA-AF7B05B7718D}">
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="5" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" style="3" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -499,14 +495,11 @@
         <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AB1" s="1"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
@@ -517,14 +510,11 @@
         <v>150</v>
       </c>
       <c r="D2">
-        <v>300</v>
-      </c>
-      <c r="E2">
         <v>400</v>
       </c>
-      <c r="AC2" s="1"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AB2" s="1"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
@@ -535,14 +525,11 @@
         <v>200</v>
       </c>
       <c r="D3">
-        <v>400</v>
-      </c>
-      <c r="E3">
         <v>150</v>
       </c>
-      <c r="AC3" s="1"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AB3" s="1"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -553,129 +540,126 @@
         <v>250</v>
       </c>
       <c r="D4">
-        <v>320</v>
-      </c>
-      <c r="E4">
         <v>460</v>
       </c>
-      <c r="AC4" s="1"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="AC6" s="1"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="AC7" s="1"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="AC8" s="1"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="AC10" s="1"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="Z12">
+      <c r="AB4" s="1"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB6" s="1"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB7" s="1"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB8" s="1"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB10" s="1"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Y12">
         <v>2020</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AA12" t="s">
         <v>1</v>
       </c>
-      <c r="AC12" s="1"/>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="Z13">
+      <c r="AB12" s="1"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Y13">
         <v>2021</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AA13" t="s">
         <v>2</v>
       </c>
-      <c r="AC13" s="1"/>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="Z14">
+      <c r="AB13" s="1"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Y14">
         <v>2022</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AA14" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="1"/>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="Z15">
+      <c r="AB14" s="1"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Y15">
         <v>2023</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AA15" t="s">
         <v>4</v>
       </c>
-      <c r="AC15" s="1"/>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="Z16">
+      <c r="AB15" s="1"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Y16">
         <v>2024</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AA16" t="s">
         <v>5</v>
       </c>
-      <c r="AC16" s="1"/>
-    </row>
-    <row r="17" spans="26:29" x14ac:dyDescent="0.25">
-      <c r="Z17">
+      <c r="AB16" s="1"/>
+    </row>
+    <row r="17" spans="25:28" x14ac:dyDescent="0.25">
+      <c r="Y17">
         <v>2025</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AA17" t="s">
         <v>6</v>
       </c>
-      <c r="AC17" s="1"/>
-    </row>
-    <row r="18" spans="26:29" x14ac:dyDescent="0.25">
-      <c r="Z18">
+      <c r="AB17" s="1"/>
+    </row>
+    <row r="18" spans="25:28" x14ac:dyDescent="0.25">
+      <c r="Y18">
         <v>2026</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AA18" t="s">
         <v>7</v>
       </c>
-      <c r="AC18" s="1"/>
-    </row>
-    <row r="19" spans="26:29" x14ac:dyDescent="0.25">
-      <c r="Z19">
+      <c r="AB18" s="1"/>
+    </row>
+    <row r="19" spans="25:28" x14ac:dyDescent="0.25">
+      <c r="Y19">
         <v>2027</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AA19" t="s">
         <v>8</v>
       </c>
-      <c r="AC19" s="1"/>
-    </row>
-    <row r="20" spans="26:29" x14ac:dyDescent="0.25">
-      <c r="Z20">
+      <c r="AB19" s="1"/>
+    </row>
+    <row r="20" spans="25:28" x14ac:dyDescent="0.25">
+      <c r="Y20">
         <v>2028</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AA20" t="s">
         <v>9</v>
       </c>
-      <c r="AC20" s="1"/>
-    </row>
-    <row r="21" spans="26:29" x14ac:dyDescent="0.25">
-      <c r="Z21">
+      <c r="AB20" s="1"/>
+    </row>
+    <row r="21" spans="25:28" x14ac:dyDescent="0.25">
+      <c r="Y21">
         <v>2029</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AA21" t="s">
         <v>10</v>
       </c>
-      <c r="AC21" s="1"/>
-    </row>
-    <row r="22" spans="26:29" x14ac:dyDescent="0.25">
-      <c r="Z22">
+      <c r="AB21" s="1"/>
+    </row>
+    <row r="22" spans="25:28" x14ac:dyDescent="0.25">
+      <c r="Y22">
         <v>2030</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AA22" t="s">
         <v>11</v>
       </c>
-      <c r="AC22" s="1"/>
-    </row>
-    <row r="23" spans="26:29" x14ac:dyDescent="0.25">
-      <c r="AB23" t="s">
+      <c r="AB22" s="1"/>
+    </row>
+    <row r="23" spans="25:28" x14ac:dyDescent="0.25">
+      <c r="AA23" t="s">
         <v>12</v>
       </c>
-      <c r="AC23" s="1"/>
+      <c r="AB23" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
